--- a/conditions/female_stimuli.xlsx
+++ b/conditions/female_stimuli.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/patrikhrabanek/Desktop/from_work_mac/Study_1/PsychoPy_experiment/creaky_experiment/conditions/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pahr0811/Documents/PhD/Year_1/Study_1/female_first_experiment/Vocal Fry Experiment #2/conditions/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1A6D0ACA-DBE0-0B4D-B4BB-9A8341F8ABAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88DCC4A0-511B-5742-B48E-A752EFBF8A17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="29040" windowHeight="17640" xr2:uid="{E94A0D02-C4AD-45DA-9BE1-25E231290689}"/>
+    <workbookView xWindow="9700" yWindow="2160" windowWidth="35160" windowHeight="21120" xr2:uid="{E94A0D02-C4AD-45DA-9BE1-25E231290689}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,136 +38,136 @@
     <t>stimFile</t>
   </si>
   <si>
-    <t>stimuli_f0/hab_f_c-1_p-3_h2_r3.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/hab_f_c-1_p2_h-3_r3.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/hab_f_c0_p-1_h-3_r3.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/hab_f_c0_p-1_h2_r2.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/hab_f_c0_p0_h-1_r3.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/hab_f_c0_p0_h-3_r2.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/hab_f_c0_p1_h0_r2.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/hab_f_c2_p-2_h2_r3.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/hab_f_c2_p1_h-3_r3.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/had_f_c-1_p-1_h-3_r1.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/had_f_c0_p-3_h2_r3.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/had_f_c1_p-1_h3_r2.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/had_f_c1_p-3_h2_r2.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/had_f_c1_p0_h1_r1.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/had_f_c2_p-2_h-3_r2.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/had_f_c2_p-3_h2_r1.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/had_f_c2_p2_h-1_r1.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/had_f_c2_p3_h-1_r1.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/tab_f_c-2_p-1_h-1_r2.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/tab_f_c-2_p0_h-1_r1.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/tab_f_c-2_p1_h-1_r2.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/tab_f_c0_p-1_h0_r1.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/tab_f_c0_p0_h3_r1.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/tab_f_c0_p2_h-1_r3.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/tab_f_c1_p-3_h-3_r1.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/tab_f_c1_p2_h3_r1.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/tab_f_c2_p3_h3_r3.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/tad_f_c-1_p-3_h-2_r1.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/tad_f_c-2_p-2_h-2_r2.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/tad_f_c0_p-1_h-3_r1.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/tad_f_c0_p-2_h0_r3.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/tad_f_c1_p-1_h1_r1.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/tad_f_c1_p-2_h1_r2.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/tad_f_c1_p0_h0_r2.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/tad_f_c2_p-2_h-1_r1.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/tad_f_c2_p1_h2_r1.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/hab_f_c0_p3_h3_r3.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/hab_f_c1_p1_h2_r2.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/had_f_c1_p2_h1_r2.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/had_f_c2_p3_h1_r2.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/tab_f_c2_p3_h0_r1.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/tab_f_c2_p3_h2_r2.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/tad_f_c0_p2_h0_r3.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/tad_f_c1_p1_h3_r1.wav</t>
+    <t>stimuli/dad_f_c-1_p0_h3_r3.wav</t>
+  </si>
+  <si>
+    <t>stimuli/dab_f_c-1_p3_h-2_r3.wav</t>
+  </si>
+  <si>
+    <t>stimuli/dab_f_c-2_p-1_h-1_r4.wav</t>
+  </si>
+  <si>
+    <t>stimuli/dab_f_c1_p-2_h-2_r3.wav</t>
+  </si>
+  <si>
+    <t>stimuli/dab_f_c1_p0_h-2_r1.wav</t>
+  </si>
+  <si>
+    <t>stimuli/dab_f_c1_p1_h-3_r1.wav</t>
+  </si>
+  <si>
+    <t>stimuli/dab_f_c1_p2_h-3_r1.wav</t>
+  </si>
+  <si>
+    <t>stimuli/dab_f_c1_p3_h-1_r4.wav</t>
+  </si>
+  <si>
+    <t>stimuli/dab_f_c1_p3_h-2_r3.wav</t>
+  </si>
+  <si>
+    <t>stimuli/dab_f_c2_p-1_h0_r3.wav</t>
+  </si>
+  <si>
+    <t>stimuli/dab_f_c2_p-1_h0_r4.wav</t>
+  </si>
+  <si>
+    <t>stimuli/dab_f_c2_p-1_h2_r2.wav</t>
+  </si>
+  <si>
+    <t>stimuli/dad_f_c-1_p2_h3_r1.wav</t>
+  </si>
+  <si>
+    <t>stimuli/dad_f_c-1_p3_h1_r1.wav</t>
+  </si>
+  <si>
+    <t>stimuli/dad_f_c-2_p0_h-2_r4.wav</t>
+  </si>
+  <si>
+    <t>stimuli/dad_f_c-2_p1_h0_r3.wav</t>
+  </si>
+  <si>
+    <t>stimuli/dad_f_c-2_p1_h3_r5.wav</t>
+  </si>
+  <si>
+    <t>stimuli/dad_f_c1_p-3_h-1_r5.wav</t>
+  </si>
+  <si>
+    <t>stimuli/dad_f_c1_p-3_h2_r4.wav</t>
+  </si>
+  <si>
+    <t>stimuli/dad_f_c1_p2_h-3_r5.wav</t>
+  </si>
+  <si>
+    <t>stimuli/dad_f_c2_p1_h3_r5.wav</t>
+  </si>
+  <si>
+    <t>stimuli/dad_f_c2_p2_h0_r3.wav</t>
+  </si>
+  <si>
+    <t>stimuli/tab_f_c-1_p-3_h-1_r3.wav</t>
+  </si>
+  <si>
+    <t>stimuli/tab_f_c-2_p0_h-2_r1.wav</t>
+  </si>
+  <si>
+    <t>stimuli/tab_f_c0_p-1_h0_r5.wav</t>
+  </si>
+  <si>
+    <t>stimuli/tab_f_c0_p3_h-1_r3.wav</t>
+  </si>
+  <si>
+    <t>stimuli/tab_f_c1_p-1_h-2_r2.wav</t>
+  </si>
+  <si>
+    <t>stimuli/tab_f_c1_p-2_h-3_r3.wav</t>
+  </si>
+  <si>
+    <t>stimuli/tab_f_c1_p-2_h-3_r4.wav</t>
+  </si>
+  <si>
+    <t>stimuli/tab_f_c1_p-3_h1_r2.wav</t>
+  </si>
+  <si>
+    <t>stimuli/tab_f_c1_p0_h0_r2.wav</t>
+  </si>
+  <si>
+    <t>stimuli/tab_f_c1_p0_h1_r1.wav</t>
+  </si>
+  <si>
+    <t>stimuli/tab_f_c1_p1_h-1_r5.wav</t>
+  </si>
+  <si>
+    <t>stimuli/tad_f_c-1_p-3_h-3_r2.wav</t>
+  </si>
+  <si>
+    <t>stimuli/tad_f_c-2_p-1_h3_r5.wav</t>
+  </si>
+  <si>
+    <t>stimuli/tad_f_c-2_p-2_h3_r1.wav</t>
+  </si>
+  <si>
+    <t>stimuli/tad_f_c1_p-1_h-1_r4.wav</t>
+  </si>
+  <si>
+    <t>stimuli/tad_f_c1_p-1_h-3_r5.wav</t>
+  </si>
+  <si>
+    <t>stimuli/tad_f_c1_p-1_h0_r2.wav</t>
+  </si>
+  <si>
+    <t>stimuli/tad_f_c1_p3_h-2_r4.wav</t>
+  </si>
+  <si>
+    <t>stimuli/tad_f_c2_p-1_h2_r3.wav</t>
+  </si>
+  <si>
+    <t>stimuli/tad_f_c2_p-2_h-1_r2.wav</t>
+  </si>
+  <si>
+    <t>stimuli/tad_f_c2_p-2_h3_r3.wav</t>
+  </si>
+  <si>
+    <t>stimuli/tad_f_c2_p0_h2_r5.wav</t>
   </si>
 </sst>
 </file>
@@ -1045,15 +1045,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100281F5302C0C8424184A8BFB4F64AD156" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a7dddae9028d61b06595b7475003a62f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="805e3853-2971-4830-a200-7929f1998a0d" xmlns:ns3="1abb6105-976e-4641-94d5-932be0f0089d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="bd95256a0d3ea48f6d8d5ce446b80fb5" ns2:_="" ns3:_="">
     <xsd:import namespace="805e3853-2971-4830-a200-7929f1998a0d"/>
@@ -1242,6 +1233,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1254,14 +1254,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C198A863-1F77-4B90-9B7E-D9A5CE4D14B1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A6E047D9-D247-4E2D-8E73-39594A3DD58C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1280,6 +1272,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C198A863-1F77-4B90-9B7E-D9A5CE4D14B1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E8FE25B-F2A6-404B-BFAA-4FDF41C79620}">
   <ds:schemaRefs>
@@ -1291,4 +1291,10 @@
     <ds:schemaRef ds:uri="1abb6105-976e-4641-94d5-932be0f0089d"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{35b66c34-d3f7-4b74-a2f5-5e46d77d2b05}" enabled="1" method="Privileged" siteId="{1e586649-7317-42fb-8949-66923d34ba7e}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>
--- a/conditions/female_stimuli.xlsx
+++ b/conditions/female_stimuli.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pahr0811/Documents/PhD/Year_1/Study_1/female_first_experiment/Vocal Fry Experiment #2/conditions/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88DCC4A0-511B-5742-B48E-A752EFBF8A17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16C41811-3B0C-934F-86C8-36800D0F0EF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9700" yWindow="2160" windowWidth="35160" windowHeight="21120" xr2:uid="{E94A0D02-C4AD-45DA-9BE1-25E231290689}"/>
   </bookViews>
@@ -38,9 +38,6 @@
     <t>stimFile</t>
   </si>
   <si>
-    <t>stimuli/dad_f_c-1_p0_h3_r3.wav</t>
-  </si>
-  <si>
     <t>stimuli/dab_f_c-1_p3_h-2_r3.wav</t>
   </si>
   <si>
@@ -74,36 +71,9 @@
     <t>stimuli/dab_f_c2_p-1_h2_r2.wav</t>
   </si>
   <si>
-    <t>stimuli/dad_f_c-1_p2_h3_r1.wav</t>
-  </si>
-  <si>
-    <t>stimuli/dad_f_c-1_p3_h1_r1.wav</t>
-  </si>
-  <si>
     <t>stimuli/dad_f_c-2_p0_h-2_r4.wav</t>
   </si>
   <si>
-    <t>stimuli/dad_f_c-2_p1_h0_r3.wav</t>
-  </si>
-  <si>
-    <t>stimuli/dad_f_c-2_p1_h3_r5.wav</t>
-  </si>
-  <si>
-    <t>stimuli/dad_f_c1_p-3_h-1_r5.wav</t>
-  </si>
-  <si>
-    <t>stimuli/dad_f_c1_p-3_h2_r4.wav</t>
-  </si>
-  <si>
-    <t>stimuli/dad_f_c1_p2_h-3_r5.wav</t>
-  </si>
-  <si>
-    <t>stimuli/dad_f_c2_p1_h3_r5.wav</t>
-  </si>
-  <si>
-    <t>stimuli/dad_f_c2_p2_h0_r3.wav</t>
-  </si>
-  <si>
     <t>stimuli/tab_f_c-1_p-3_h-1_r3.wav</t>
   </si>
   <si>
@@ -168,6 +138,36 @@
   </si>
   <si>
     <t>stimuli/tad_f_c2_p0_h2_r5.wav</t>
+  </si>
+  <si>
+    <t>stimuli/dad_f_c2_p1_h1_r1.wav</t>
+  </si>
+  <si>
+    <t>stimuli/dad_f_c2_p-3_h2_r3.wav</t>
+  </si>
+  <si>
+    <t>stimuli/dad_f_c1_p2_h-3_r3.wav</t>
+  </si>
+  <si>
+    <t>stimuli/dad_f_c1_p1_h0_r4.wav</t>
+  </si>
+  <si>
+    <t>stimuli/dad_f_c0_p3_h-1_r3.wav</t>
+  </si>
+  <si>
+    <t>stimuli/dad_f_c0_p-3_h2_r5.wav</t>
+  </si>
+  <si>
+    <t>stimuli/dad_f_c-2_p2_h2_r4.wav</t>
+  </si>
+  <si>
+    <t>stimuli/dad_f_c-2_p1_h3_r4.wav</t>
+  </si>
+  <si>
+    <t>stimuli/dad_f_c-1_p0_h-1_r1.wav</t>
+  </si>
+  <si>
+    <t>stimuli/dad_f_c-1_p-2_h-1_r4.wav</t>
   </si>
 </sst>
 </file>
@@ -875,167 +875,167 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1045,6 +1045,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100281F5302C0C8424184A8BFB4F64AD156" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a7dddae9028d61b06595b7475003a62f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="805e3853-2971-4830-a200-7929f1998a0d" xmlns:ns3="1abb6105-976e-4641-94d5-932be0f0089d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="bd95256a0d3ea48f6d8d5ce446b80fb5" ns2:_="" ns3:_="">
     <xsd:import namespace="805e3853-2971-4830-a200-7929f1998a0d"/>
@@ -1233,15 +1242,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1254,6 +1254,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C198A863-1F77-4B90-9B7E-D9A5CE4D14B1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A6E047D9-D247-4E2D-8E73-39594A3DD58C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1268,14 +1276,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C198A863-1F77-4B90-9B7E-D9A5CE4D14B1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
